--- a/data/demo/AEK-Traffic-2026-07-20~2026-07-20.xlsx
+++ b/data/demo/AEK-Traffic-2026-07-20~2026-07-20.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="73">
   <si>
     <t>2026-07-20</t>
   </si>
@@ -23,19 +23,19 @@
     <t>AEK-CYBER Barra de sonido para TV, dos altavoces de 2 pulgadas con imán de 45 + dos membranas para graves, sonido claro ≥75dB, Bluetooth inalámbrico y conexiones coaxial/AUX, diseño compacto de 81.2cm, sistema de sonido envolvente para Smart TV, adecuado para cine en casa/PC/juegos/fiestas</t>
   </si>
   <si>
-    <t>6078</t>
-  </si>
-  <si>
-    <t>4543</t>
-  </si>
-  <si>
-    <t>254</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>4.18%</t>
+    <t>9040</t>
+  </si>
+  <si>
+    <t>6741</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>333</t>
+  </si>
+  <si>
+    <t>4.07%</t>
   </si>
   <si>
     <t>605237091919950</t>
@@ -44,19 +44,19 @@
     <t>Barra de Sonido Bluetooth 1 Pieza con Luces RGB Rítmicas Sonido Estéreo Graves Potentes Compatible con Tarjeta TF USB Radio FM Entrada AUX Función TWS y Llamadas Manos Libres Batería de Larga Duración Carga Tipo-C Altavoz Compacto para Escritorio Gamer Hogar Oficina Celular y Televisor</t>
   </si>
   <si>
-    <t>8640</t>
-  </si>
-  <si>
-    <t>6616</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>196</t>
-  </si>
-  <si>
-    <t>2.53%</t>
+    <t>12841</t>
+  </si>
+  <si>
+    <t>9769</t>
+  </si>
+  <si>
+    <t>330</t>
+  </si>
+  <si>
+    <t>294</t>
+  </si>
+  <si>
+    <t>2.57%</t>
   </si>
   <si>
     <t>602380552791635</t>
@@ -65,16 +65,16 @@
     <t>Audífonos Alámbricos AEK CYBER - In - Ear Estéreo con Micrófono, Manos Libres, Control por Botones, TYPE-C Compatible con For Android, Celulares, Tablets - Ideal para Música, Videos, Llamadas y Deportes</t>
   </si>
   <si>
-    <t>448</t>
-  </si>
-  <si>
-    <t>338</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>1.56%</t>
+    <t>644</t>
+  </si>
+  <si>
+    <t>485</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>1.40%</t>
   </si>
   <si>
     <t>602278882831514</t>
@@ -83,145 +83,154 @@
     <t>Cargador de auto AEK CYBER con doble puerto USB, cargador de mechero de carro resistente al calor, carga rápida de 12W, voltaje de salida estable de 12 - 24V para proteger dispositivos, adaptador compatible con dispositivos móviles, tabletas, audífonos y GPS</t>
   </si>
   <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>137</t>
+    <t>241</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>2.49%</t>
+  </si>
+  <si>
+    <t>602287472782701</t>
+  </si>
+  <si>
+    <t>Cargador de coche AEK CYBER resistente al calor, incluye cable de carga USB-C de alta calidad, carga rápida de 15,5 W, enchufe USB para automóvil (12-24 V), doble puerto USB, compatible con dispositivos móviles, tabletas, auriculares y sistemas de navegación GPS.</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>40</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>0.60%</t>
-  </si>
-  <si>
-    <t>602287472782701</t>
-  </si>
-  <si>
-    <t>Cargador de coche AEK CYBER resistente al calor, incluye cable de carga USB-C de alta calidad, carga rápida de 15,5 W, enchufe USB para automóvil (12-24 V), doble puerto USB, compatible con dispositivos móviles, tabletas, auriculares y sistemas de navegación GPS.</t>
+    <t>1.89%</t>
+  </si>
+  <si>
+    <t>602712674510786</t>
+  </si>
+  <si>
+    <t>1 Pieza, Auriculares Inalámbricos AEK CYBER BT 5.4 – Material ABS Resistente, Sonido HiFi, Autonomía de 15 Horas, Control Táctil Inteligente,Diseño de apariencia translúcida- Ideal para Hogar, Viajes y como Regalo para Jóvenes</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0.00%</t>
+  </si>
+  <si>
+    <t>602727706887090</t>
+  </si>
+  <si>
+    <t>AEK CYBER - Power bank ultra delgado de 10000mAh con dos puertos USB 3.0 (5V/2.1A), indicador de carga, cable USB-C incluido, compatible con teléfonos, tablets y dispositivos electrónicos portátiles, ideal para viajes.</t>
   </si>
   <si>
     <t>35</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>2.86%</t>
-  </si>
-  <si>
-    <t>602712674510786</t>
-  </si>
-  <si>
-    <t>1 Pieza, Auriculares Inalámbricos AEK CYBER BT 5.4 – Material ABS Resistente, Sonido HiFi, Autonomía de 15 Horas, Control Táctil Inteligente,Diseño de apariencia translúcida- Ideal para Hogar, Viajes y como Regalo para Jóvenes</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>0.00%</t>
-  </si>
-  <si>
-    <t>602727706887090</t>
-  </si>
-  <si>
-    <t>AEK CYBER - Power bank ultra delgado de 10000mAh con dos puertos USB 3.0 (5V/2.1A), indicador de carga, cable USB-C incluido, compatible con teléfonos, tablets y dispositivos electrónicos portátiles, ideal para viajes.</t>
+    <t>33</t>
+  </si>
+  <si>
+    <t>603028354608966</t>
+  </si>
+  <si>
+    <t>1 Pieza, Auriculares Inalámbricos AEK CYBER BT 5.4 – Material ABS Resistente, Sonido HiFi, ANC, Autonomía de 16 Horas, Control Táctil Inteligente - Ideal para Hogar, Viajes y como Regalo para Jóvenes</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>603095463461603</t>
+  </si>
+  <si>
+    <t>Power Bank Portátil AEK CYBER - 10,000 mAh！Carga Rápida 22.5W. Salidas USB 3.0 y USB Type - C, Indicador de Carga. ¡Incluye Cable USB - C Gratis! Compatible con Teléfonos, Tabletasy Dispositivos Electrónicos. Ideal para Viajes</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>603140023770196</t>
+  </si>
+  <si>
+    <t>1 Pieza Auriculares Inalámbricos AEK CYBER - Sonido HiFi, ANC, Caja de Carga con Gran Capacidad, Autonomía de 16 Horas, Control Táctil Inteligente. ¡Ideal para Hogar, Viajes y como Regalo para Jóvenes!</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>604861231908854</t>
+  </si>
+  <si>
+    <t>AEK CYBER Altavoz Bluetooth Portátil con Sonido Hi-Fi, Luces de Baile RGB, Conexión TWS y Radio FM, Multifuncional para KTV/Aire Libre/Fiestas, Diseño Compacto con Soporte para Teléfono</t>
+  </si>
+  <si>
+    <t>911</t>
+  </si>
+  <si>
+    <t>729</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>2.52%</t>
+  </si>
+  <si>
+    <t>604898057881398</t>
+  </si>
+  <si>
+    <t>Altavoz Inalámbrico Portátil con Diseño Retro, Bajos Optimizados y Sonido 3D Envolvente,Compatible con TF/FM/AUX, Conexión BT TWS. Ideal para Home Theater, Fiestas y Regalos​</t>
+  </si>
+  <si>
+    <t>1528</t>
+  </si>
+  <si>
+    <t>1245</t>
+  </si>
+  <si>
+    <t>27</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>603028354608966</t>
-  </si>
-  <si>
-    <t>1 Pieza, Auriculares Inalámbricos AEK CYBER BT 5.4 – Material ABS Resistente, Sonido HiFi, ANC, Autonomía de 16 Horas, Control Táctil Inteligente - Ideal para Hogar, Viajes y como Regalo para Jóvenes</t>
-  </si>
-  <si>
-    <t>603095463461603</t>
-  </si>
-  <si>
-    <t>Power Bank Portátil AEK CYBER - 10,000 mAh！Carga Rápida 22.5W. Salidas USB 3.0 y USB Type - C, Indicador de Carga. ¡Incluye Cable USB - C Gratis! Compatible con Teléfonos, Tabletasy Dispositivos Electrónicos. Ideal para Viajes</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>603140023770196</t>
-  </si>
-  <si>
-    <t>1 Pieza Auriculares Inalámbricos AEK CYBER - Sonido HiFi, ANC, Caja de Carga con Gran Capacidad, Autonomía de 16 Horas, Control Táctil Inteligente. ¡Ideal para Hogar, Viajes y como Regalo para Jóvenes!</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>604861231908854</t>
-  </si>
-  <si>
-    <t>AEK CYBER Altavoz Bluetooth Portátil con Sonido Hi-Fi, Luces de Baile RGB, Conexión TWS y Radio FM, Multifuncional para KTV/Aire Libre/Fiestas, Diseño Compacto con Soporte para Teléfono</t>
-  </si>
-  <si>
-    <t>612</t>
-  </si>
-  <si>
-    <t>491</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>3.10%</t>
-  </si>
-  <si>
-    <t>604898057881398</t>
-  </si>
-  <si>
-    <t>Altavoz Inalámbrico Portátil con Diseño Retro, Bajos Optimizados y Sonido 3D Envolvente,Compatible con TF/FM/AUX, Conexión BT TWS. Ideal para Home Theater, Fiestas y Regalos​</t>
-  </si>
-  <si>
-    <t>1034</t>
-  </si>
-  <si>
-    <t>838</t>
+    <t>1.77%</t>
+  </si>
+  <si>
+    <t>605126228031397</t>
+  </si>
+  <si>
+    <t>AEK-CYBER Altavoz de Bajo Inalámbrico Portátil con Subwoofer y Doble Altavoz Estéreo, Luces LED de Color Variable. Ideal para Hogar, Coche y Uso Exterior. Un Regalo Perfecto para los Amantes de la Música al Aire Libre</t>
+  </si>
+  <si>
+    <t>422</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
-    <t>1.55%</t>
-  </si>
-  <si>
-    <t>605126228031397</t>
-  </si>
-  <si>
-    <t>AEK-CYBER Altavoz de Bajo Inalámbrico Portátil con Subwoofer y Doble Altavoz Estéreo, Luces LED de Color Variable. Ideal para Hogar, Coche y Uso Exterior. Un Regalo Perfecto para los Amantes de la Música al Aire Libre</t>
-  </si>
-  <si>
-    <t>261</t>
-  </si>
-  <si>
-    <t>227</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>3.83%</t>
+    <t>3.55%</t>
   </si>
 </sst>
 </file>
@@ -444,10 +453,10 @@
         <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -455,25 +464,25 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -481,25 +490,25 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
@@ -507,25 +516,25 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" t="s">
         <v>39</v>
-      </c>
-      <c r="E8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="9">
@@ -533,25 +542,25 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -559,25 +568,25 @@
         <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
@@ -585,25 +594,25 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H11" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
@@ -611,25 +620,25 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G12" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H12" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -637,25 +646,25 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="G13" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14">
@@ -663,25 +672,25 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G14" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H14" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
